--- a/data/trans_orig/IP33A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>44947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>36076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>51998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>31286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69626</t>
+          <t>68779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>139942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27979</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47682</t>
+          <t>47802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74799</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58993</t>
+          <t>59988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49320</t>
+          <t>49605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98136</t>
+          <t>97599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119876</t>
+          <t>119231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>49952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91250</t>
+          <t>89713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116897</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86325</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78001</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95217</t>
+          <t>95572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150189</t>
+          <t>151455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175836</t>
+          <t>177373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39816</t>
+          <t>40194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57631</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84483</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111115</t>
+          <t>109538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72940</t>
+          <t>72445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90511</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71833</t>
+          <t>71963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89846</t>
+          <t>90681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148676</t>
+          <t>150253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175308</t>
+          <t>175478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>27941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>26454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>51449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31498</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45534</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>86400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>132385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163245</t>
+          <t>161853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132159</t>
+          <t>132506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216730</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>247590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>17886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44519</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41220</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77084</t>
+          <t>76204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74629</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113970</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74565</t>
+          <t>74093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63275</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99139</t>
+          <t>100336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128689</t>
+          <t>128776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168030</t>
+          <t>167161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44751</t>
+          <t>45320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60388</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98421</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150496</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102286</t>
+          <t>102045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136138</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>190727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>233861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP33A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6436</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7671</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12324</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17512</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26321</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22072</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28494</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22731</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28432</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15514</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12182</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17470</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44947</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18760</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18760</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18760</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29743</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29743</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29743</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18760</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18760</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24435</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18666</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30815</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19576</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13991</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24993</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13930</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24569</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>43,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24435</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18126</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29904</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35143</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28763</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40912</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25701</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20284</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31286</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20708</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>31347</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>56,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35143</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>29674</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41452</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>69255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59578</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59578</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59578</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45277</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>45277</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>45277</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>59578</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>59578</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>59578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11755</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15692</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8146</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4871</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12288</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11935</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11755</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8274</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9483</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13169</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16235</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12093</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12446</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19680</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>66,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9483</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5649</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12964</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21238</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21238</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21238</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24381</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>24381</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>24381</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21238</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21238</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39436</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31989</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49008</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>31145</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23815</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38629</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24082</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38980</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>39436</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32140</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48135</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>67587</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>68255</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60771</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75585</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60420</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>75318</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>60140</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>51441</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>67436</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117666</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139942</t>
+          <t>138998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>99400</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4267</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8337</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6672</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3515</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11135</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3573</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10785</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4267</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1468</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8727</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -2444,67 +2444,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>16606</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12536</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19241</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>16752</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19909</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19851</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>71,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16606</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12146</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19405</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>37773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23424</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>23424</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>23424</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20873</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20873</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24853</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18213</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32911</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>39577</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31608</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47802</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31669</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47547</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>43,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17236</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31734</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53704</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56486</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48428</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>63126</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52019</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43794</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59988</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44049</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59927</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>56,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>56486</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49605</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>64103</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>98091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119231</t>
+          <t>118635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>81339</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>81339</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>81339</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>91596</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>91596</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>91596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>81339</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>81339</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>81339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15094</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10235</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19735</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12873</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8863</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15962</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8468</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16313</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15094</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10843</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19745</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33874</t>
+          <t>33499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18703</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8043</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12053</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12448</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13844</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9193</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18095</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28938</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28938</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28938</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20916</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>20916</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>20916</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28938</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28938</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44214</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35778</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53820</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>59122</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49952</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68870</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>69104</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>43,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35578</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89713</t>
+          <t>89683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115631</t>
+          <t>116325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86936</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77330</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76814</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>67066</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85984</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>66832</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86188</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86936</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>77319</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95572</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151455</t>
+          <t>150761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177373</t>
+          <t>177403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131150</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131150</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131150</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>135936</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131150</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131150</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131150</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3875</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7126</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6966</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21899</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19405</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23118</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10989</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7738</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13071</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13149</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21899</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19090</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23118</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>35576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23118</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23118</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23118</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14864</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>14864</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>14864</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23118</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23118</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48739</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39521</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>58008</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48517</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40194</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57882</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>40649</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57743</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48739</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38783</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57501</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84313</t>
+          <t>84370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109538</t>
+          <t>110729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80725</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71456</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89943</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>81810</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72445</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>90133</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72584</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>89678</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80725</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71963</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90681</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150253</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175478</t>
+          <t>175421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>129464</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>129464</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>129464</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>130327</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>130327</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>130327</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>129464</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>129464</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>129464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21133</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15857</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26456</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22991</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17435</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27941</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17577</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>28372</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21133</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15874</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26454</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18781</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13458</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19297</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14347</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13916</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24711</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>45,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18781</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13460</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>24040</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45784</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39914</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39914</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39914</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>42288</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>42288</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>42288</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39914</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,107 +4958,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71091</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61208</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82567</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>75384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65082</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86400</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>64356</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85615</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71091</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>59990</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82457</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>146475</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>130916</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>42,84%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>146475</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>132385</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>161853</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5071,107 +5071,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121405</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109929</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>131288</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>112095</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>101079</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>122397</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101864</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123123</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>121405</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>110039</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>132506</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>63,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>54,33%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>233500</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>217177</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>249059</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>57,16%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>233500</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>218122</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>247590</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187479</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10016</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6827</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11334</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7571</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12972</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>84,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23175</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16843</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16843</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16843</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13461</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13461</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13461</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47693</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36204</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65440</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35720</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28208</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>43906</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54570</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76204</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90290</t>
+          <t>79606</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75498</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113883</t>
+          <t>99552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59494</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88730</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>66581</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58395</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74093</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>67570</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64155</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100336</t>
+          <t>75140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152369</t>
+          <t>144811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>124865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167161</t>
+          <t>159142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>124934</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>124934</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>124934</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>102301</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>102301</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>102301</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140359</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140359</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140359</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>242659</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>242659</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242659</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12675</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8089</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18137</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12195</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16647</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,84%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21490</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16028</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15202</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10750</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19644</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31159</t>
+          <t>30003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>43303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34165</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34165</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34165</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27397</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27397</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27397</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>64841</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64841</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64841</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66682</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54366</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84014</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50041</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41113</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>60145</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>37189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97439</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>125542</t>
+          <t>113114</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105823</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148957</t>
+          <t>135046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>109260</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91928</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>121576</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>93117</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83013</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102045</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>92331</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99087</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190727</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233861</t>
+          <t>215863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
